--- a/kbl/teaching/qt-intent-sample.xlsx
+++ b/kbl/teaching/qt-intent-sample.xlsx
@@ -9,12 +9,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t xml:space="preserve">undefined</t>
   </si>
   <si>
-    <t xml:space="preserve">math-g1-up-u01-k001</t>
+    <t xml:space="preserve">math-g1-up-u02-k001</t>
   </si>
   <si>
     <t xml:space="preserve">(needs-review 补样)</t>
@@ -26,7 +26,7 @@
     <t xml:space="preserve">needs-review</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「1-5数的认识」（5以内数的认识和加、减法 · 认、读、写1—5各数； 知道1—5的顺序（从前往后1、2、3、4、5，从后往前5、4、3、2、1）； 理解数的含义，能用实物表示；初步区分基数（表示数量）与序数（表示顺序）； 掌握“一一对应”的比较方法；能用“多”“少”“同样多”描述数量关系）：认、读、写1—5各数</t>
+    <t xml:space="preserve">训练「6和10的认识」（6～10的认识和加、减法 · 数的认识、大小比较、加减法运算及运用。10以内数的分解（凑十法的基础）、加减法运算及运用。）：数的认识、大小比较、加减法运算及运用</t>
   </si>
   <si>
     <t xml:space="preserve">calc（计算题，计算操作）选取依据——数值表征：本知识点为数值表征，与计算题的算式形态一致</t>
@@ -83,18 +83,15 @@
     <t xml:space="preserve">成立：认知层级「认识」落于choice认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
   </si>
   <si>
-    <t xml:space="preserve">math-g1-up-u01-k003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「0的认识和加减法」（5以内数的认识和加、减法 · 理解减法是从整体中去掉一部分的运算；掌握5以内减法的口算方法；能根据情境图列减法算式。）：理解减法是从整体中去掉一部分的运算</t>
-  </si>
-  <si>
     <t xml:space="preserve">math-g1-up-u03-k001</t>
   </si>
   <si>
     <t xml:space="preserve">geometry</t>
   </si>
   <si>
+    <t xml:space="preserve">confirmed</t>
+  </si>
+  <si>
     <t xml:space="preserve">训练「立体图形初识」（认识立体图形 · 直观认识长方体、正方体、圆柱、球等立体图形的特征）：直观认识长方体、正方体、圆柱、球等立体图形的特征</t>
   </si>
   <si>
@@ -146,6 +143,60 @@
     <t xml:space="preserve">成立：认知层级「认识」落于choice认知区间[认识/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
   </si>
   <si>
+    <t xml:space="preserve">math-g1-up-u03-k002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「生活中的立体图形」（认识立体图形 · 经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）：经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g1-up-u04-k001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「11—20数的认识」（11～20的认识 · 数数（一个一个数、两个两个数等）、数的读写、大小比较）：数数（一个一个数、两个两个数等）、数的读写、大小比较</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g1-up-u05-k001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「凑十法」（20以内的进位加法 · 运用“凑十法”灵活计算）：运用“凑十法”灵活计算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「分析」在apply题型认知区间[理解/应用/分析]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「分析」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g1-up-u05-k003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「解决问题」（20以内的进位加法 · 能根据情境图提出并解决用加法计算的实际问题）：能根据情境图提出并解决用加法计算的实际问题</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g1-up-u06-k001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「综合运用本册知识」（复习与关联 · 熟练掌握以上知识点）：熟练掌握以上知识点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「分析」在apply题型认知区间[理解/应用/分析]内；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：choice、fill。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；fill属书面表达而本题型属综合应用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill（填空题，书面表达）选取依据——情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、choice。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、fill。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；fill属书面表达而本题型属辨认判断</t>
+  </si>
+  <si>
     <t xml:space="preserve">math-g1-down-u01-k001</t>
   </si>
   <si>
@@ -161,12 +212,6 @@
     <t xml:space="preserve">训练「运算方法（平十、破十）」（20以内的退位减法 · 掌握“破十法”“平十法”“想加算减”等计算方法 运用多种算法灵活计算）：掌握“破十法”“平十法”“想加算减”等计算方法 运用多种算法灵活计算</t>
   </si>
   <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「分析」在apply题型认知区间[理解/应用/分析]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「分析」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
     <t xml:space="preserve">math-g1-down-u02-k002</t>
   </si>
   <si>
@@ -197,31 +242,154 @@
     <t xml:space="preserve">成立：认知层级「应用」落于choice认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
   </si>
   <si>
-    <t xml:space="preserve">math-g1-down-u02-k003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「解决问题」（20以内的退位减法 · 能解决“有多余条件”的实际问题，以及“求一个数比另一个数多几（或少几）”的问题）：能解决“有多余条件”的实际问题，以及“求一个数比另一个数多几（或少几）”的问题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u03-k004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「数位」（100以内数的认识 · 认识个位、十位、百位，理解各数位的意义）：认识个位、十位、百位，理解各数位的意义</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u04-k005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「解决问题」（100以内的口算加、减法 · 能用加、减法解决实际问题）：能用加、减法解决实际问题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u06-k002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「图形表述数量关系」（数量间的加减关系 · 借助画图等策略理解数量间的加减关系）：借助画图等策略理解数量间的加减关系</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calc（计算题，计算操作）选取依据——认知匹配：本知识点认知层级「理解」在calc题型认知区间[了解/理解/应用]内</t>
+    <t xml:space="preserve">math-g1-down-u07-k001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">application-word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「认识人民币的单位」（欢乐购物街 · 元、角、分。）：元、角、分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——表征支持：本知识点含图形表征，apply题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill（填空题，书面表达）选取依据——表征支持：本知识点含图形表征，fill题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「认识」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g1-down-u07-k002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「人民币换算」（欢乐购物街 · 知道1元=10角，1角=10分，会进行100元以内人民币之间的简单换算）：知道1元=10角，1角=10分，会进行100元以内人民币之间的简单换算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「应用」在apply题型认知区间[理解/应用/分析]内；表征支持：本知识点含图形表征，apply题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「应用」落于apply认知区间[理解/应用/分析]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「应用」在fill题型认知区间[了解/理解/应用]内；表征支持：本知识点含图形表征，fill题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「应用」落于fill认知区间[了解/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「应用」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「应用」落于choice认知区间[认识/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g2-up-u01-k001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「分类的含义」（分类与整理 · 根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）：根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「理解」在fill题型认知区间[了解/理解/应用]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、classify、judge。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于fill认知区间[了解/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在choice题型认知区间[认识/理解/应用]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、classify、fill、judge。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；classify属分类整理而本题型属辨认判断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于choice认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「理解」在apply题型认知区间[理解/应用/分析]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：choice、classify、fill、judge。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；classify属分类整理而本题型属综合应用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">classify</t>
+  </si>
+  <si>
+    <t xml:space="preserve">classify（分类整理题，分类整理）选取依据——认知匹配：本知识点认知层级「理解」在classify题型认知区间[认识/理解/应用]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、fill、judge。本题型差异——apply属综合应用而本题型属分类整理；choice属辨认判断而本题型属分类整理；choice含干扰项（辨认成分重）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">风险（classify）：若分组元素可被单一表面特征（数值大小）分组，退化为排序/计算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于classify认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">judge（判断题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在judge题型认知区间[认识/理解]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、classify、fill。本题型差异——apply属综合应用而本题型属辨认判断；apply认知跨度[理解/应用/分析]与本题型[认识/理解]不同；choice含干扰项（辨认成分重）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于judge认知区间[认识/理解]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g2-up-u01-k002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「单一标准分类」（分类与整理 · 先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组。）：先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组</t>
+  </si>
+  <si>
+    <t xml:space="preserve">classify（分类整理题，分类整理）选取依据——认知匹配：本知识点认知层级「应用」在classify题型认知区间[认识/理解/应用]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「应用」落于classify认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g2-down-u02-k001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multiplication-division</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「有余数除法的含义」（有余数的除法 · 平均分物品时，有时会有剩余，剩余的部分叫做余数）：平均分物品时，有时会有剩余，剩余的部分叫做余数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calc（计算题，计算操作）选取依据——认知匹配：本知识点认知层级「理解」在calc题型认知区间[了解/理解/应用]内；数值表征：本知识点为数值表征，与计算题的算式形态一致</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于calc认知区间[了解/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g2-down-u02-k002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「余数和除数的关系」（有余数的除法 · 核心规则：**余数＜除数**；被除数 = 商 × 除数 + 余数）：核心规则：**余数＜除数**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g2-down-u02-k004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「解决问题」（有余数的除法 · 能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份）；去尾法：购物、裁剪材料（剩余不足一份直接舍弃））：能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">math-g2-down-u02-k005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">训练「周期问题」（有余数的除法 · 利用有余数除法找图形、彩旗排列规律）：利用有余数除法找图形、彩旗排列规律</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calc（计算题，计算操作）选取依据——认知匹配：本知识点认知层级「应用」在calc题型认知区间[了解/理解/应用]内</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、choice、fill、geometry。本题型差异——apply属综合应用而本题型属计算操作；apply支持图形；choice属辨认判断而本题型属计算操作</t>
@@ -233,196 +401,31 @@
     <t xml:space="preserve">representation-conflict</t>
   </si>
   <si>
-    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「理解」在fill题型认知区间[了解/理解/应用]内；表征支持：本知识点含图形表征，fill题型支持图形呈现</t>
+    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「应用」在fill题型认知区间[了解/理解/应用]内；表征支持：本知识点含图形表征，fill题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、calc、choice、geometry。本题型差异——apply属综合应用而本题型属书面表达；calc属计算操作而本题型属书面表达；calc仅文字/算式</t>
   </si>
   <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于fill认知区间[了解/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「理解」在apply题型认知区间[理解/应用/分析]内；表征支持：本知识点含图形表征，apply题型支持图形呈现</t>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「应用」在apply题型认知区间[理解/应用/分析]内；表征支持：本知识点含图形表征，apply题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：calc、choice、fill、geometry。本题型差异——calc属计算操作而本题型属综合应用；calc仅文字/算式；choice属辨认判断而本题型属综合应用</t>
   </si>
   <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于apply认知区间[理解/应用/分析]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现</t>
+    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「应用」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、calc、fill、geometry。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；calc属计算操作而本题型属辨认判断</t>
   </si>
   <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于choice认知区间[认识/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geometry（操作/作图题，图形操作）选取依据——认知匹配：本知识点认知层级「理解」在geometry题型认知区间[认识/理解/应用/分析]内；表征支持：本知识点含图形表征，geometry题型支持图形呈现</t>
+    <t xml:space="preserve">geometry（操作/作图题，图形操作）选取依据——认知匹配：本知识点认知层级「应用」在geometry题型认知区间[认识/理解/应用/分析]内；表征支持：本知识点含图形表征，geometry题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、calc、choice、fill。本题型差异——apply属综合应用而本题型属图形操作；apply带情境；apply认知跨度[理解/应用/分析]与本题型[认识/理解/应用/分析]不同</t>
   </si>
   <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于geometry认知区间[认识/理解/应用/分析]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u06-k003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「比多少、多步加减运算应用题」（数量间的加减关系 · 能解决“比多比少”以及多步加减关系的实际问题）：能解决“比多比少”以及多步加减关系的实际问题</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u07-k001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">application-word</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「认识人民币的单位」（欢乐购物街 · 元、角、分。）：元、角、分</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——表征支持：本知识点含图形表征，apply题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：choice、fill。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；fill属书面表达而本题型属综合应用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill（填空题，书面表达）选取依据——表征支持：本知识点含图形表征，fill题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、choice。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「认识」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、fill。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；fill属书面表达而本题型属辨认判断</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u07-k002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「人民币换算」（欢乐购物街 · 知道1元=10角，1角=10分，会进行100元以内人民币之间的简单换算）：知道1元=10角，1角=10分，会进行100元以内人民币之间的简单换算</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「应用」在apply题型认知区间[理解/应用/分析]内；表征支持：本知识点含图形表征，apply题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「应用」落于apply认知区间[理解/应用/分析]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「应用」在fill题型认知区间[了解/理解/应用]内；表征支持：本知识点含图形表征，fill题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「应用」落于fill认知区间[了解/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「应用」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现；情境支持：综合与实践域知识点适合有情境载体的题型</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「应用」落于choice认知区间[认识/理解/应用]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g1-down-u08-k001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「综合运用本册知识」（复习与关联 · 对全册知识进行系统梳理，涵盖数与运算、图形的认识、数量关系等模块，进行综合应用与复习巩固）：对全册知识进行系统梳理，涵盖数与运算、图形的认识、数量关系等模块，进行综合应用与复习巩固</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g2-up-u01-k001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「分类的含义」（分类与整理 · 根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）：根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「理解」在fill题型认知区间[了解/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、classify、judge。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于fill认知区间[了解/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在choice题型认知区间[认识/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、classify、fill、judge。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；classify属分类整理而本题型属辨认判断</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于choice认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「理解」在apply题型认知区间[理解/应用/分析]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：choice、classify、fill、judge。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；classify属分类整理而本题型属综合应用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">classify</t>
-  </si>
-  <si>
-    <t xml:space="preserve">classify（分类整理题，分类整理）选取依据——认知匹配：本知识点认知层级「理解」在classify题型认知区间[认识/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、fill、judge。本题型差异——apply属综合应用而本题型属分类整理；choice属辨认判断而本题型属分类整理；choice含干扰项（辨认成分重）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">风险（classify）：若分组元素可被单一表面特征（数值大小）分组，退化为排序/计算</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于classify认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">judge（判断题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在judge题型认知区间[认识/理解]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、classify、fill。本题型差异——apply属综合应用而本题型属辨认判断；apply认知跨度[理解/应用/分析]与本题型[认识/理解]不同；choice含干扰项（辨认成分重）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于judge认知区间[认识/理解]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g2-up-u01-k002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「单一标准分类」（分类与整理 · 先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组。）：先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组</t>
-  </si>
-  <si>
-    <t xml:space="preserve">classify（分类整理题，分类整理）选取依据——认知匹配：本知识点认知层级「应用」在classify题型认知区间[认识/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「应用」落于classify认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g2-down-u02-k001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">multiplication-division</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「有余数除法的含义」（有余数的除法 · 平均分物品时，有时会有剩余，剩余的部分叫做余数）：平均分物品时，有时会有剩余，剩余的部分叫做余数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calc（计算题，计算操作）选取依据——认知匹配：本知识点认知层级「理解」在calc题型认知区间[了解/理解/应用]内；数值表征：本知识点为数值表征，与计算题的算式形态一致</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于calc认知区间[了解/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">math-g2-down-u02-k002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">训练「余数和除数的关系」（有余数的除法 · 核心规则：**余数＜除数**；被除数 = 商 × 除数 + 余数）：核心规则：**余数＜除数**</t>
+    <t xml:space="preserve">成立：认知层级「应用」落于geometry认知区间[认识/理解/应用/分析]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
   </si>
   <si>
     <t xml:space="preserve">math-g3-up-u08-k001</t>
@@ -663,31 +666,31 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" t="s">
         <v>9</v>
@@ -701,22 +704,22 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
         <v>13</v>
@@ -725,7 +728,7 @@
         <v>9</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
         <v>9</v>
@@ -739,22 +742,22 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
         <v>17</v>
@@ -763,7 +766,7 @@
         <v>9</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
         <v>9</v>
@@ -777,28 +780,28 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="J9" t="s">
         <v>9</v>
@@ -812,31 +815,31 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J10" t="s">
         <v>9</v>
@@ -850,34 +853,34 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
         <v>28</v>
       </c>
-      <c r="F11" t="s">
-        <v>33</v>
-      </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" t="s">
         <v>9</v>
@@ -888,28 +891,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I12" t="s">
         <v>9</v>
@@ -926,34 +929,34 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="J13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K13" t="s">
         <v>9</v>
@@ -964,31 +967,31 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J14" t="s">
         <v>9</v>
@@ -1002,31 +1005,31 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J15" t="s">
         <v>9</v>
@@ -1040,28 +1043,28 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I16" t="s">
         <v>9</v>
@@ -1078,34 +1081,34 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I17" t="s">
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K17" t="s">
         <v>9</v>
@@ -1116,34 +1119,34 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K18" t="s">
         <v>9</v>
@@ -1154,10 +1157,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -1166,19 +1169,19 @@
         <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
         <v>9</v>
@@ -1192,10 +1195,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -1230,10 +1233,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1268,10 +1271,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
@@ -1306,10 +1309,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
@@ -1347,19 +1350,19 @@
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E24" t="s">
         <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="G24" t="s">
         <v>7</v>
@@ -1368,10 +1371,10 @@
         <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="J24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K24" t="s">
         <v>9</v>
@@ -1385,19 +1388,19 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E25" t="s">
         <v>53</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="G25" t="s">
         <v>12</v>
@@ -1406,10 +1409,10 @@
         <v>13</v>
       </c>
       <c r="I25" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K25" t="s">
         <v>9</v>
@@ -1423,7 +1426,7 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
         <v>15</v>
@@ -1435,7 +1438,7 @@
         <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G26" t="s">
         <v>16</v>
@@ -1444,7 +1447,7 @@
         <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
@@ -1461,19 +1464,19 @@
         <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E27" t="s">
         <v>53</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>
@@ -1482,10 +1485,10 @@
         <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K27" t="s">
         <v>9</v>
@@ -1496,34 +1499,34 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="G28" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="H28" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="J28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K28" t="s">
         <v>9</v>
@@ -1534,7 +1537,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -1546,13 +1549,13 @@
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="H29" t="s">
         <v>13</v>
@@ -1561,7 +1564,7 @@
         <v>9</v>
       </c>
       <c r="J29" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K29" t="s">
         <v>9</v>
@@ -1572,34 +1575,34 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="F30" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="H30" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="J30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K30" t="s">
         <v>9</v>
@@ -1613,31 +1616,31 @@
         <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
         <v>63</v>
       </c>
       <c r="F31" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I31" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="J31" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K31" t="s">
         <v>9</v>
@@ -1648,28 +1651,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G32" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="H32" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I32" t="s">
         <v>9</v>
@@ -1686,34 +1689,34 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
         <v>9</v>
       </c>
       <c r="J33" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K33" t="s">
         <v>9</v>
@@ -1724,34 +1727,34 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="H34" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="J34" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K34" t="s">
         <v>9</v>
@@ -1762,31 +1765,31 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J35" t="s">
         <v>9</v>
@@ -1800,19 +1803,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F36" t="s">
         <v>6</v>
@@ -1838,19 +1841,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -1876,10 +1879,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
@@ -1888,7 +1891,7 @@
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F38" t="s">
         <v>50</v>
@@ -1914,19 +1917,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
@@ -1952,34 +1955,34 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E40" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" t="s">
         <v>69</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
+        <v>7</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I40" t="s">
         <v>70</v>
       </c>
-      <c r="G40" t="s">
-        <v>71</v>
-      </c>
-      <c r="H40" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40" t="s">
-        <v>9</v>
-      </c>
       <c r="J40" t="s">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="K40" t="s">
         <v>9</v>
@@ -1990,31 +1993,31 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G41" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="H41" t="s">
         <v>13</v>
       </c>
       <c r="I41" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J41" t="s">
         <v>9</v>
@@ -2028,31 +2031,31 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G42" t="s">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
@@ -2066,31 +2069,31 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F43" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="J43" t="s">
         <v>9</v>
@@ -2104,34 +2107,34 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F44" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="H44" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="J44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K44" t="s">
         <v>9</v>
@@ -2142,28 +2145,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B45" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F45" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="H45" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I45" t="s">
         <v>9</v>
@@ -2180,34 +2183,34 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F46" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I46" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="J46" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K46" t="s">
         <v>9</v>
@@ -2218,31 +2221,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="J47" t="s">
         <v>9</v>
@@ -2256,34 +2259,34 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" t="s">
         <v>87</v>
       </c>
-      <c r="F48" t="s">
-        <v>9</v>
-      </c>
       <c r="G48" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I48" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="J48" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K48" t="s">
         <v>9</v>
@@ -2294,34 +2297,34 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B49" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" t="s">
         <v>89</v>
       </c>
-      <c r="C49" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" t="s">
-        <v>4</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="G49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
         <v>90</v>
       </c>
-      <c r="F49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G49" t="s">
-        <v>92</v>
-      </c>
-      <c r="H49" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" t="s">
-        <v>9</v>
-      </c>
       <c r="J49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K49" t="s">
         <v>9</v>
@@ -2332,34 +2335,34 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
       </c>
       <c r="I50" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="J50" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K50" t="s">
         <v>9</v>
@@ -2370,31 +2373,31 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F51" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G51" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="J51" t="s">
         <v>9</v>
@@ -2408,31 +2411,31 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F52" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -2446,31 +2449,31 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F53" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G53" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="I53" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J53" t="s">
         <v>9</v>
@@ -2484,31 +2487,31 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B54" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F54" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G54" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="H54" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I54" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="J54" t="s">
         <v>9</v>
@@ -2522,34 +2525,34 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F55" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G55" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I55" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="J55" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K55" t="s">
         <v>9</v>
@@ -2560,34 +2563,34 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G56" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="J56" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K56" t="s">
         <v>9</v>
@@ -2598,31 +2601,31 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B57" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F57" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G57" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="J57" t="s">
         <v>9</v>
@@ -2636,31 +2639,31 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F58" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G58" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H58" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="I58" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J58" t="s">
         <v>9</v>
@@ -2674,34 +2677,34 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
+        <v>112</v>
+      </c>
+      <c r="F59" t="s">
+        <v>9</v>
+      </c>
+      <c r="G59" t="s">
         <v>109</v>
       </c>
-      <c r="F59" t="s">
-        <v>113</v>
-      </c>
-      <c r="G59" t="s">
-        <v>114</v>
-      </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="J59" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K59" t="s">
         <v>9</v>
@@ -2712,31 +2715,31 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B60" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F60" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G60" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -2750,31 +2753,31 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B61" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C61" t="s">
-        <v>119</v>
+        <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F61" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="G61" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="H61" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="I61" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="J61" t="s">
         <v>9</v>
@@ -2788,31 +2791,31 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F62" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="G62" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="H62" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="J62" t="s">
         <v>9</v>
@@ -2826,31 +2829,31 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F63" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="G63" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="H63" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="J63" t="s">
         <v>9</v>
@@ -2864,31 +2867,31 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B64" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C64" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F64" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G64" t="s">
-        <v>114</v>
+        <v>7</v>
       </c>
       <c r="H64" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I64" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="J64" t="s">
         <v>9</v>
@@ -2902,31 +2905,31 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B65" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F65" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G65" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="H65" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I65" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J65" t="s">
         <v>9</v>
@@ -2940,31 +2943,31 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>119</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F66" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>121</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="J66" t="s">
         <v>9</v>
@@ -2978,34 +2981,34 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F67" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>125</v>
+        <v>21</v>
       </c>
       <c r="H67" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="J67" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K67" t="s">
         <v>9</v>
@@ -3016,22 +3019,22 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B68" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C68" t="s">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F68" t="s">
-        <v>134</v>
+        <v>6</v>
       </c>
       <c r="G68" t="s">
         <v>7</v>
@@ -3040,10 +3043,10 @@
         <v>8</v>
       </c>
       <c r="I68" t="s">
-        <v>135</v>
+        <v>9</v>
       </c>
       <c r="J68" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K68" t="s">
         <v>9</v>
@@ -3054,22 +3057,22 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B69" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C69" t="s">
         <v>11</v>
       </c>
       <c r="D69" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F69" t="s">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="G69" t="s">
         <v>12</v>
@@ -3078,10 +3081,10 @@
         <v>13</v>
       </c>
       <c r="I69" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="J69" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K69" t="s">
         <v>9</v>
@@ -3092,10 +3095,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B70" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C70" t="s">
         <v>15</v>
@@ -3104,10 +3107,10 @@
         <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F70" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="G70" t="s">
         <v>16</v>
@@ -3116,7 +3119,7 @@
         <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="J70" t="s">
         <v>9</v>
@@ -3130,22 +3133,22 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="F71" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="G71" t="s">
         <v>21</v>
@@ -3154,10 +3157,10 @@
         <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K71" t="s">
         <v>9</v>
@@ -3168,34 +3171,34 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C72" t="s">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F72" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="G72" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="H72" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="I72" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="J72" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="K72" t="s">
         <v>9</v>
@@ -3206,10 +3209,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -3218,19 +3221,19 @@
         <v>19</v>
       </c>
       <c r="E73" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F73" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="G73" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
       </c>
       <c r="I73" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="J73" t="s">
         <v>9</v>
@@ -3244,10 +3247,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C74" t="s">
         <v>15</v>
@@ -3256,19 +3259,19 @@
         <v>19</v>
       </c>
       <c r="E74" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="J74" t="s">
         <v>9</v>
@@ -3282,10 +3285,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
@@ -3294,19 +3297,19 @@
         <v>19</v>
       </c>
       <c r="E75" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
       <c r="G75" t="s">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="H75" t="s">
         <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="J75" t="s">
         <v>9</v>
@@ -3320,34 +3323,34 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" t="s">
+        <v>125</v>
+      </c>
+      <c r="F76" t="s">
+        <v>136</v>
+      </c>
+      <c r="G76" t="s">
+        <v>137</v>
+      </c>
+      <c r="H76" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" t="s">
         <v>138</v>
       </c>
-      <c r="B76" t="s">
-        <v>139</v>
-      </c>
-      <c r="C76" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" t="s">
-        <v>4</v>
-      </c>
-      <c r="E76" t="s">
-        <v>140</v>
-      </c>
-      <c r="F76" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" t="s">
-        <v>7</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
-      </c>
-      <c r="I76" t="s">
-        <v>9</v>
-      </c>
       <c r="J76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K76" t="s">
         <v>9</v>
@@ -3358,34 +3361,34 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B77" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C77" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F77" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G77" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H77" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I77" t="s">
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K77" t="s">
         <v>9</v>
@@ -3396,28 +3399,28 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B78" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H78" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I78" t="s">
         <v>9</v>
@@ -3434,34 +3437,34 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B79" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C79" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G79" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H79" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J79" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K79" t="s">
         <v>9</v>
@@ -3472,34 +3475,34 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>139</v>
+      </c>
+      <c r="B80" t="s">
+        <v>140</v>
+      </c>
+      <c r="C80" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
         <v>141</v>
       </c>
-      <c r="B80" t="s">
-        <v>139</v>
-      </c>
-      <c r="C80" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" t="s">
-        <v>4</v>
-      </c>
-      <c r="E80" t="s">
-        <v>142</v>
-      </c>
       <c r="F80" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I80" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K80" t="s">
         <v>9</v>
@@ -3510,34 +3513,34 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B81" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F81" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G81" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H81" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I81" t="s">
         <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K81" t="s">
         <v>9</v>
@@ -3548,28 +3551,28 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H82" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I82" t="s">
         <v>9</v>
@@ -3586,34 +3589,34 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B83" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C83" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E83" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G83" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J83" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K83" t="s">
         <v>9</v>
@@ -3624,34 +3627,34 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>142</v>
+      </c>
+      <c r="B84" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" t="s">
         <v>143</v>
       </c>
-      <c r="B84" t="s">
-        <v>144</v>
-      </c>
-      <c r="C84" t="s">
-        <v>3</v>
-      </c>
-      <c r="D84" t="s">
-        <v>4</v>
-      </c>
-      <c r="E84" t="s">
-        <v>145</v>
-      </c>
       <c r="F84" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I84" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K84" t="s">
         <v>9</v>
@@ -3662,34 +3665,34 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G85" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H85" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I85" t="s">
         <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K85" t="s">
         <v>9</v>
@@ -3700,28 +3703,28 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B86" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H86" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I86" t="s">
         <v>9</v>
@@ -3738,34 +3741,34 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B87" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C87" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H87" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J87" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K87" t="s">
         <v>9</v>
@@ -3776,31 +3779,31 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
+        <v>144</v>
+      </c>
+      <c r="B88" t="s">
+        <v>145</v>
+      </c>
+      <c r="C88" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" t="s">
         <v>146</v>
       </c>
-      <c r="B88" t="s">
-        <v>144</v>
-      </c>
-      <c r="C88" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" t="s">
-        <v>147</v>
-      </c>
       <c r="F88" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H88" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I88" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="J88" t="s">
         <v>9</v>
@@ -3814,31 +3817,31 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B89" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C89" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G89" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H89" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J89" t="s">
         <v>9</v>
@@ -3852,31 +3855,31 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B90" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G90" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I90" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J90" t="s">
         <v>9</v>
@@ -3890,31 +3893,31 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B91" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C91" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F91" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J91" t="s">
         <v>9</v>
@@ -3928,34 +3931,34 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>147</v>
+      </c>
+      <c r="B92" t="s">
+        <v>145</v>
+      </c>
+      <c r="C92" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" t="s">
         <v>148</v>
       </c>
-      <c r="B92" t="s">
-        <v>149</v>
-      </c>
-      <c r="C92" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" t="s">
-        <v>4</v>
-      </c>
-      <c r="E92" t="s">
-        <v>150</v>
-      </c>
       <c r="F92" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G92" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I92" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="J92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K92" t="s">
         <v>9</v>
@@ -3966,34 +3969,34 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C93" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E93" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F93" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G93" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H93" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I93" t="s">
         <v>9</v>
       </c>
       <c r="J93" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K93" t="s">
         <v>9</v>
@@ -4004,34 +4007,34 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B94" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F94" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H94" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I94" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="J94" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K94" t="s">
         <v>9</v>
@@ -4042,34 +4045,34 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F95" t="s">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="G95" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H95" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="J95" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K95" t="s">
         <v>9</v>
@@ -4080,34 +4083,34 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" t="s">
+        <v>150</v>
+      </c>
+      <c r="C96" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" t="s">
         <v>151</v>
       </c>
-      <c r="B96" t="s">
-        <v>149</v>
-      </c>
-      <c r="C96" t="s">
-        <v>3</v>
-      </c>
-      <c r="D96" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" t="s">
-        <v>152</v>
-      </c>
       <c r="F96" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H96" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I96" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="J96" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K96" t="s">
         <v>9</v>
@@ -4118,31 +4121,31 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F97" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="G97" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H97" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="J97" t="s">
         <v>9</v>
@@ -4156,31 +4159,31 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B98" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C98" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F98" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I98" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
@@ -4194,39 +4197,77 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B99" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C99" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" t="s">
+        <v>26</v>
+      </c>
+      <c r="E99" t="s">
+        <v>153</v>
+      </c>
+      <c r="F99" t="s">
+        <v>73</v>
+      </c>
+      <c r="G99" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" t="s">
+        <v>74</v>
+      </c>
+      <c r="J99" t="s">
+        <v>9</v>
+      </c>
+      <c r="K99" t="s">
+        <v>9</v>
+      </c>
+      <c r="L99" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>152</v>
+      </c>
+      <c r="B100" t="s">
+        <v>150</v>
+      </c>
+      <c r="C100" t="s">
         <v>18</v>
       </c>
-      <c r="D99" t="s">
-        <v>19</v>
-      </c>
-      <c r="E99" t="s">
-        <v>152</v>
-      </c>
-      <c r="F99" t="s">
-        <v>60</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s">
+        <v>153</v>
+      </c>
+      <c r="F100" t="s">
+        <v>75</v>
+      </c>
+      <c r="G100" t="s">
         <v>21</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H100" t="s">
         <v>22</v>
       </c>
-      <c r="I99" t="s">
-        <v>61</v>
-      </c>
-      <c r="J99" t="s">
-        <v>9</v>
-      </c>
-      <c r="K99" t="s">
-        <v>9</v>
-      </c>
-      <c r="L99" t="s">
+      <c r="I100" t="s">
+        <v>76</v>
+      </c>
+      <c r="J100" t="s">
+        <v>9</v>
+      </c>
+      <c r="K100" t="s">
+        <v>9</v>
+      </c>
+      <c r="L100" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4240,42 +4281,42 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/kbl/teaching/qt-intent-sample.xlsx
+++ b/kbl/teaching/qt-intent-sample.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
   <si>
     <t xml:space="preserve">undefined</t>
   </si>
@@ -203,6 +203,15 @@
     <t xml:space="preserve">训练「平面图形认识」（认识平面图形 · 直观认识长方形、正方形、三角形、圆、平行四边形，知道名称并能辨认和区分 体会“面在体上”——平面图形可以从立体图形上得到 会用平面图形进行简单的拼组）：直观认识长方形、正方形、三角形、圆、平行四边形，知道名称并能辨认和区分 体会“面在体上”——平面图形可以从立体图形上得到 会用平面图形进行简单的拼组</t>
   </si>
   <si>
+    <t xml:space="preserve">用判断题辨析平面图形的名称与基本特征（边、形、直观属性），巩固「面在体上」的关系判断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实质依据：judge 可对图形名称与特征做正误辨析，配合图形呈现探查直观认识层级；不承载拼组考查</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立（限定）：judge 在本 KP 仅限「名称与特征辨析」用途，明确不承载拼组子目标（拼组由 apply/geometry 题型承载）</t>
+  </si>
+  <si>
     <t xml:space="preserve">math-g1-down-u02-k001</t>
   </si>
   <si>
@@ -210,6 +219,18 @@
   </si>
   <si>
     <t xml:space="preserve">训练「运算方法（平十、破十）」（20以内的退位减法 · 掌握“破十法”“平十法”“想加算减”等计算方法 运用多种算法灵活计算）：掌握“破十法”“平十法”“想加算减”等计算方法 运用多种算法灵活计算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">在解决问题情境中选用破十法/平十法/想加算减并说明理由——考查方法的选择与迁移；方法本身的操练由平十、破十的竖式计算（calc）与填空（fill）承载</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实质依据：apply 的情境迫使学生对「用哪种方法」做分析性决策（对应 analyze 层级）；与 calc/fill 的方法操练形成「操练—迁移」分工</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calc/fill 承载平十、破十的竖式计算与填空操练（方法本身）；apply 与之的差异=在真实情境中选择并迁移方法（方法选择型应用题）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立（限定）：仅限「方法运用型」应用题表述，不复述方法定义</t>
   </si>
   <si>
     <t xml:space="preserve">math-g1-down-u02-k002</t>
@@ -1736,13 +1757,13 @@
         <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G34" t="s">
         <v>38</v>
@@ -1751,7 +1772,7 @@
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="J34" t="s">
         <v>9</v>
@@ -1803,10 +1824,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
@@ -1815,7 +1836,7 @@
         <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F36" t="s">
         <v>6</v>
@@ -1841,10 +1862,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -1853,7 +1874,7 @@
         <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
@@ -1879,31 +1900,31 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
         <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="J38" t="s">
         <v>9</v>
@@ -1917,10 +1938,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -1929,7 +1950,7 @@
         <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
@@ -1955,10 +1976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
@@ -1967,10 +1988,10 @@
         <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s">
         <v>7</v>
@@ -1979,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s">
         <v>9</v>
@@ -1993,10 +2014,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
@@ -2005,10 +2026,10 @@
         <v>26</v>
       </c>
       <c r="E41" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -2017,7 +2038,7 @@
         <v>13</v>
       </c>
       <c r="I41" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J41" t="s">
         <v>9</v>
@@ -2031,10 +2052,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
         <v>15</v>
@@ -2043,10 +2064,10 @@
         <v>26</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F42" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s">
         <v>16</v>
@@ -2055,7 +2076,7 @@
         <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
@@ -2069,10 +2090,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
@@ -2081,10 +2102,10 @@
         <v>26</v>
       </c>
       <c r="E43" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F43" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s">
         <v>21</v>
@@ -2093,7 +2114,7 @@
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J43" t="s">
         <v>9</v>
@@ -2107,10 +2128,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C44" t="s">
         <v>15</v>
@@ -2119,10 +2140,10 @@
         <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s">
         <v>57</v>
@@ -2145,10 +2166,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
@@ -2157,10 +2178,10 @@
         <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F45" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s">
         <v>59</v>
@@ -2183,10 +2204,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
@@ -2195,10 +2216,10 @@
         <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F46" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s">
         <v>61</v>
@@ -2221,10 +2242,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
         <v>15</v>
@@ -2233,10 +2254,10 @@
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G47" t="s">
         <v>57</v>
@@ -2245,7 +2266,7 @@
         <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J47" t="s">
         <v>9</v>
@@ -2259,10 +2280,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
@@ -2271,10 +2292,10 @@
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F48" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s">
         <v>59</v>
@@ -2283,7 +2304,7 @@
         <v>13</v>
       </c>
       <c r="I48" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J48" t="s">
         <v>9</v>
@@ -2297,10 +2318,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
@@ -2309,10 +2330,10 @@
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F49" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G49" t="s">
         <v>61</v>
@@ -2321,7 +2342,7 @@
         <v>22</v>
       </c>
       <c r="I49" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J49" t="s">
         <v>9</v>
@@ -2335,10 +2356,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
@@ -2347,19 +2368,19 @@
         <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F50" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G50" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H50" t="s">
         <v>13</v>
       </c>
       <c r="I50" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J50" t="s">
         <v>9</v>
@@ -2373,10 +2394,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
@@ -2385,19 +2406,19 @@
         <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F51" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G51" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J51" t="s">
         <v>9</v>
@@ -2411,10 +2432,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
         <v>15</v>
@@ -2423,19 +2444,19 @@
         <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G52" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -2449,31 +2470,31 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F53" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G53" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H53" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I53" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="J53" t="s">
         <v>9</v>
@@ -2487,10 +2508,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
         <v>36</v>
@@ -2499,19 +2520,19 @@
         <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F54" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G54" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H54" t="s">
         <v>39</v>
       </c>
       <c r="I54" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="J54" t="s">
         <v>9</v>
@@ -2525,10 +2546,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
@@ -2537,19 +2558,19 @@
         <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G55" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H55" t="s">
         <v>13</v>
       </c>
       <c r="I55" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J55" t="s">
         <v>9</v>
@@ -2563,10 +2584,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
@@ -2575,19 +2596,19 @@
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F56" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G56" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J56" t="s">
         <v>9</v>
@@ -2601,10 +2622,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C57" t="s">
         <v>15</v>
@@ -2613,19 +2634,19 @@
         <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F57" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J57" t="s">
         <v>9</v>
@@ -2639,31 +2660,31 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D58" t="s">
         <v>26</v>
       </c>
       <c r="E58" t="s">
+        <v>119</v>
+      </c>
+      <c r="F58" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" t="s">
         <v>112</v>
       </c>
-      <c r="F58" t="s">
+      <c r="H58" t="s">
         <v>113</v>
       </c>
-      <c r="G58" t="s">
-        <v>105</v>
-      </c>
-      <c r="H58" t="s">
-        <v>106</v>
-      </c>
       <c r="I58" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J58" t="s">
         <v>9</v>
@@ -2677,10 +2698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B59" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
         <v>36</v>
@@ -2689,13 +2710,13 @@
         <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="H59" t="s">
         <v>39</v>
@@ -2715,10 +2736,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
@@ -2727,10 +2748,10 @@
         <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G60" t="s">
         <v>7</v>
@@ -2739,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -2753,10 +2774,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
@@ -2765,10 +2786,10 @@
         <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F61" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G61" t="s">
         <v>12</v>
@@ -2777,7 +2798,7 @@
         <v>13</v>
       </c>
       <c r="I61" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J61" t="s">
         <v>9</v>
@@ -2791,10 +2812,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C62" t="s">
         <v>15</v>
@@ -2803,10 +2824,10 @@
         <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F62" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G62" t="s">
         <v>16</v>
@@ -2815,7 +2836,7 @@
         <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J62" t="s">
         <v>9</v>
@@ -2829,10 +2850,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
@@ -2841,10 +2862,10 @@
         <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G63" t="s">
         <v>21</v>
@@ -2853,7 +2874,7 @@
         <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J63" t="s">
         <v>9</v>
@@ -2867,10 +2888,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B64" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
@@ -2879,10 +2900,10 @@
         <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
@@ -2891,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="I64" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J64" t="s">
         <v>9</v>
@@ -2905,10 +2926,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
@@ -2917,10 +2938,10 @@
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F65" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G65" t="s">
         <v>12</v>
@@ -2929,7 +2950,7 @@
         <v>13</v>
       </c>
       <c r="I65" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J65" t="s">
         <v>9</v>
@@ -2943,10 +2964,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C66" t="s">
         <v>15</v>
@@ -2955,10 +2976,10 @@
         <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s">
         <v>16</v>
@@ -2967,7 +2988,7 @@
         <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J66" t="s">
         <v>9</v>
@@ -2981,10 +3002,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C67" t="s">
         <v>18</v>
@@ -2993,10 +3014,10 @@
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F67" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s">
         <v>21</v>
@@ -3005,7 +3026,7 @@
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J67" t="s">
         <v>9</v>
@@ -3019,7 +3040,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
@@ -3031,7 +3052,7 @@
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -3057,7 +3078,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
@@ -3069,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -3095,7 +3116,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
@@ -3107,7 +3128,7 @@
         <v>19</v>
       </c>
       <c r="E70" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F70" t="s">
         <v>50</v>
@@ -3133,7 +3154,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
@@ -3145,7 +3166,7 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
@@ -3171,7 +3192,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -3183,22 +3204,22 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F72" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G72" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H72" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I72" t="s">
         <v>9</v>
       </c>
       <c r="J72" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="K72" t="s">
         <v>9</v>
@@ -3209,7 +3230,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B73" t="s">
         <v>2</v>
@@ -3221,19 +3242,19 @@
         <v>19</v>
       </c>
       <c r="E73" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G73" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H73" t="s">
         <v>13</v>
       </c>
       <c r="I73" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J73" t="s">
         <v>9</v>
@@ -3247,7 +3268,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B74" t="s">
         <v>2</v>
@@ -3259,19 +3280,19 @@
         <v>19</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F74" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G74" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="J74" t="s">
         <v>9</v>
@@ -3285,7 +3306,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
@@ -3297,19 +3318,19 @@
         <v>19</v>
       </c>
       <c r="E75" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F75" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G75" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H75" t="s">
         <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J75" t="s">
         <v>9</v>
@@ -3323,7 +3344,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
@@ -3335,19 +3356,19 @@
         <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F76" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G76" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H76" t="s">
         <v>30</v>
       </c>
       <c r="I76" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J76" t="s">
         <v>9</v>
@@ -3361,10 +3382,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B77" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
@@ -3373,7 +3394,7 @@
         <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -3399,10 +3420,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B78" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -3411,7 +3432,7 @@
         <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -3437,10 +3458,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B79" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C79" t="s">
         <v>15</v>
@@ -3449,7 +3470,7 @@
         <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -3475,10 +3496,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B80" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
@@ -3487,7 +3508,7 @@
         <v>26</v>
       </c>
       <c r="E80" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F80" t="s">
         <v>20</v>
@@ -3513,10 +3534,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C81" t="s">
         <v>3</v>
@@ -3525,7 +3546,7 @@
         <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -3551,10 +3572,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -3563,7 +3584,7 @@
         <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -3589,10 +3610,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B83" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C83" t="s">
         <v>15</v>
@@ -3601,7 +3622,7 @@
         <v>26</v>
       </c>
       <c r="E83" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -3627,10 +3648,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
@@ -3639,7 +3660,7 @@
         <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F84" t="s">
         <v>20</v>
@@ -3665,10 +3686,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C85" t="s">
         <v>3</v>
@@ -3677,7 +3698,7 @@
         <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -3703,10 +3724,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B86" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -3715,7 +3736,7 @@
         <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -3741,10 +3762,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B87" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C87" t="s">
         <v>15</v>
@@ -3753,7 +3774,7 @@
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
@@ -3779,10 +3800,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
@@ -3791,7 +3812,7 @@
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F88" t="s">
         <v>20</v>
@@ -3817,10 +3838,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B89" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C89" t="s">
         <v>3</v>
@@ -3829,10 +3850,10 @@
         <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F89" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -3841,7 +3862,7 @@
         <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J89" t="s">
         <v>9</v>
@@ -3855,10 +3876,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B90" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -3867,10 +3888,10 @@
         <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F90" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s">
         <v>12</v>
@@ -3879,7 +3900,7 @@
         <v>13</v>
       </c>
       <c r="I90" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J90" t="s">
         <v>9</v>
@@ -3893,10 +3914,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B91" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C91" t="s">
         <v>15</v>
@@ -3905,10 +3926,10 @@
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F91" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s">
         <v>16</v>
@@ -3917,7 +3938,7 @@
         <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J91" t="s">
         <v>9</v>
@@ -3931,10 +3952,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B92" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
@@ -3943,10 +3964,10 @@
         <v>26</v>
       </c>
       <c r="E92" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F92" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G92" t="s">
         <v>21</v>
@@ -3955,7 +3976,7 @@
         <v>22</v>
       </c>
       <c r="I92" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J92" t="s">
         <v>9</v>
@@ -3969,10 +3990,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C93" t="s">
         <v>3</v>
@@ -3981,7 +4002,7 @@
         <v>26</v>
       </c>
       <c r="E93" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -4007,10 +4028,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B94" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -4019,7 +4040,7 @@
         <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -4045,10 +4066,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B95" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
         <v>15</v>
@@ -4057,7 +4078,7 @@
         <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F95" t="s">
         <v>50</v>
@@ -4083,10 +4104,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B96" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
@@ -4095,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F96" t="s">
         <v>9</v>
@@ -4121,10 +4142,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B97" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C97" t="s">
         <v>3</v>
@@ -4133,10 +4154,10 @@
         <v>26</v>
       </c>
       <c r="E97" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F97" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s">
         <v>7</v>
@@ -4145,7 +4166,7 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="J97" t="s">
         <v>9</v>
@@ -4159,10 +4180,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -4171,10 +4192,10 @@
         <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F98" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G98" t="s">
         <v>12</v>
@@ -4183,7 +4204,7 @@
         <v>13</v>
       </c>
       <c r="I98" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
@@ -4197,10 +4218,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B99" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C99" t="s">
         <v>15</v>
@@ -4209,10 +4230,10 @@
         <v>26</v>
       </c>
       <c r="E99" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F99" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G99" t="s">
         <v>16</v>
@@ -4221,7 +4242,7 @@
         <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J99" t="s">
         <v>9</v>
@@ -4235,10 +4256,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B100" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
@@ -4247,10 +4268,10 @@
         <v>26</v>
       </c>
       <c r="E100" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="F100" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G100" t="s">
         <v>21</v>
@@ -4259,7 +4280,7 @@
         <v>22</v>
       </c>
       <c r="I100" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J100" t="s">
         <v>9</v>
@@ -4281,42 +4302,42 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/kbl/teaching/qt-intent-sample.xlsx
+++ b/kbl/teaching/qt-intent-sample.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t xml:space="preserve">undefined</t>
   </si>
@@ -26,7 +26,7 @@
     <t xml:space="preserve">needs-review</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「6和10的认识」（6～10的认识和加、减法 · 数的认识、大小比较、加减法运算及运用。10以内数的分解（凑十法的基础）、加减法运算及运用。）：数的认识、大小比较、加减法运算及运用</t>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「6和10的认识」（数的认识、大小比较、加减法运算及运用）；题型限定：不承载概念表述与图形操作</t>
   </si>
   <si>
     <t xml:space="preserve">calc（计算题，计算操作）选取依据——数值表征：本知识点为数值表征，与计算题的算式形态一致</t>
@@ -47,6 +47,9 @@
     <t xml:space="preserve">fill</t>
   </si>
   <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「6和10的认识」（数的认识、大小比较、加减法运算及运用）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、calc、choice。本题型差异——apply属综合应用而本题型属书面表达；calc属计算操作而本题型属书面表达；calc仅文字/算式</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
     <t xml:space="preserve">apply</t>
   </si>
   <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「6和10的认识」（数的认识、大小比较、加减法运算及运用）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
     <t xml:space="preserve">同 KP 其他允许题型：calc、choice、fill。本题型差异——calc属计算操作而本题型属综合应用；calc仅文字/算式；choice属辨认判断而本题型属综合应用</t>
   </si>
   <si>
@@ -71,6 +77,9 @@
     <t xml:space="preserve">ai-verified</t>
   </si>
   <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「6和10的认识」（数的认识、大小比较、加减法运算及运用）；题型限定：不承载完整的书写与计算过程</t>
+  </si>
+  <si>
     <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「认识」在choice题型认知区间[认识/理解/应用]内</t>
   </si>
   <si>
@@ -146,19 +155,46 @@
     <t xml:space="preserve">math-g1-up-u03-k002</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「生活中的立体图形」（认识立体图形 · 经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）：经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识</t>
+    <t xml:space="preserve">通过geometry（操作/作图题）训练图形操作与直观辨认，对象为「生活中的立体图形」（经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）；题型限定：不承载脱离图形的纯文字表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「生活中的立体图形」（经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「生活中的立体图形」（经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过judge（判断题）训练特征与关系的正误辨析，对象为「生活中的立体图形」（经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）；题型限定：不承载操作性任务与多步应用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「生活中的立体图形」（经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识，经历从实物到图形、由具体到一般的抽象过程，形成对立体图形的直观认识）；题型限定：不承载完整的书写与计算过程</t>
   </si>
   <si>
     <t xml:space="preserve">math-g1-up-u04-k001</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「11—20数的认识」（11～20的认识 · 数数（一个一个数、两个两个数等）、数的读写、大小比较）：数数（一个一个数、两个两个数等）、数的读写、大小比较</t>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「11—20数的认识」（数数（一个一个数、两个两个数等）、数的读写、大小比较）；题型限定：不承载概念表述与图形操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「11—20数的认识」（数数（一个一个数、两个两个数等）、数的读写、大小比较）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「11—20数的认识」（数数（一个一个数、两个两个数等）、数的读写、大小比较）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「11—20数的认识」（数数（一个一个数、两个两个数等）、数的读写、大小比较）；题型限定：不承载完整的书写与计算过程</t>
   </si>
   <si>
     <t xml:space="preserve">math-g1-up-u05-k001</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「凑十法」（20以内的进位加法 · 运用“凑十法”灵活计算）：运用“凑十法”灵活计算</t>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「凑十法」（运用“凑十法”灵活计算）；题型限定：不承载概念表述与图形操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「凑十法」（运用“凑十法”灵活计算）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「凑十法」（运用“凑十法”灵活计算）；题型限定：不承载方法定义的复述</t>
   </si>
   <si>
     <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「分析」在apply题型认知区间[理解/应用/分析]内</t>
@@ -167,16 +203,28 @@
     <t xml:space="preserve">成立：认知层级「分析」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
   </si>
   <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「凑十法」（运用“凑十法”灵活计算）；题型限定：不承载完整的书写与计算过程</t>
+  </si>
+  <si>
     <t xml:space="preserve">math-g1-up-u05-k003</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「解决问题」（20以内的进位加法 · 能根据情境图提出并解决用加法计算的实际问题）：能根据情境图提出并解决用加法计算的实际问题</t>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「解决问题」（能根据情境图提出并解决用加法计算的实际问题）；题型限定：不承载概念表述与图形操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「解决问题」（能根据情境图提出并解决用加法计算的实际问题）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「解决问题」（能根据情境图提出并解决用加法计算的实际问题）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「解决问题」（能根据情境图提出并解决用加法计算的实际问题）；题型限定：不承载完整的书写与计算过程</t>
   </si>
   <si>
     <t xml:space="preserve">math-g1-up-u06-k001</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「综合运用本册知识」（复习与关联 · 熟练掌握以上知识点）：熟练掌握以上知识点</t>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「综合运用本册知识」（熟练掌握以上知识点）；题型限定：不承载方法定义的复述</t>
   </si>
   <si>
     <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「分析」在apply题型认知区间[理解/应用/分析]内；情境支持：综合与实践域知识点适合有情境载体的题型</t>
@@ -185,12 +233,18 @@
     <t xml:space="preserve">同 KP 其他允许题型：choice、fill。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；fill属书面表达而本题型属综合应用</t>
   </si>
   <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「综合运用本册知识」（熟练掌握以上知识点）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
     <t xml:space="preserve">fill（填空题，书面表达）选取依据——情境支持：综合与实践域知识点适合有情境载体的题型</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、choice。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
   </si>
   <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「综合运用本册知识」（熟练掌握以上知识点）；题型限定：不承载完整的书写与计算过程</t>
+  </si>
+  <si>
     <t xml:space="preserve">choice（选择题，辨认判断）选取依据——情境支持：综合与实践域知识点适合有情境载体的题型</t>
   </si>
   <si>
@@ -401,13 +455,22 @@
     <t xml:space="preserve">math-g2-down-u02-k004</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「解决问题」（有余数的除法 · 能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份）；去尾法：购物、裁剪材料（剩余不足一份直接舍弃））：能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份）</t>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「解决问题」（能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份））；题型限定：不承载概念表述与图形操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「解决问题」（能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份））；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「解决问题」（能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份））；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「解决问题」（能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份））；题型限定：不承载完整的书写与计算过程</t>
   </si>
   <si>
     <t xml:space="preserve">math-g2-down-u02-k005</t>
   </si>
   <si>
-    <t xml:space="preserve">训练「周期问题」（有余数的除法 · 利用有余数除法找图形、彩旗排列规律）：利用有余数除法找图形、彩旗排列规律</t>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载概念表述与图形操作</t>
   </si>
   <si>
     <t xml:space="preserve">calc（计算题，计算操作）选取依据——认知匹配：本知识点认知层级「应用」在calc题型认知区间[了解/理解/应用]内</t>
@@ -422,22 +485,34 @@
     <t xml:space="preserve">representation-conflict</t>
   </si>
   <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
     <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「应用」在fill题型认知区间[了解/理解/应用]内；表征支持：本知识点含图形表征，fill题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、calc、choice、geometry。本题型差异——apply属综合应用而本题型属书面表达；calc属计算操作而本题型属书面表达；calc仅文字/算式</t>
   </si>
   <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
     <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「应用」在apply题型认知区间[理解/应用/分析]内；表征支持：本知识点含图形表征，apply题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：calc、choice、fill、geometry。本题型差异——calc属计算操作而本题型属综合应用；calc仅文字/算式；choice属辨认判断而本题型属综合应用</t>
   </si>
   <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载完整的书写与计算过程</t>
+  </si>
+  <si>
     <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「应用」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现</t>
   </si>
   <si>
     <t xml:space="preserve">同 KP 其他允许题型：apply、calc、fill、geometry。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；calc属计算操作而本题型属辨认判断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过geometry（操作/作图题）训练图形操作与直观辨认，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载脱离图形的纯文字表述</t>
   </si>
   <si>
     <t xml:space="preserve">geometry（操作/作图题，图形操作）选取依据——认知匹配：本知识点认知层级「应用」在geometry题型认知区间[认识/理解/应用/分析]内；表征支持：本知识点含图形表征，geometry题型支持图形呈现</t>
@@ -582,22 +657,22 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
         <v>9</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
         <v>9</v>
@@ -614,28 +689,28 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" t="s">
         <v>9</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
         <v>9</v>
@@ -652,25 +727,25 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
         <v>9</v>
@@ -684,31 +759,31 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
         <v>9</v>
@@ -722,28 +797,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>9</v>
@@ -760,28 +835,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
         <v>9</v>
@@ -798,31 +873,31 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J9" t="s">
         <v>9</v>
@@ -836,31 +911,31 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J10" t="s">
         <v>9</v>
@@ -874,31 +949,31 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J11" t="s">
         <v>9</v>
@@ -912,7 +987,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -924,16 +999,16 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" t="s">
         <v>9</v>
@@ -950,28 +1025,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I13" t="s">
         <v>9</v>
@@ -988,31 +1063,31 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J14" t="s">
         <v>9</v>
@@ -1026,31 +1101,31 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
         <v>45</v>
       </c>
-      <c r="F15" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" t="s">
-        <v>42</v>
-      </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J15" t="s">
         <v>9</v>
@@ -1064,7 +1139,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -1076,7 +1151,7 @@
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -1102,7 +1177,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1114,22 +1189,22 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" t="s">
         <v>9</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="s">
         <v>9</v>
@@ -1140,34 +1215,34 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="F18" t="s">
         <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" t="s">
         <v>9</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" t="s">
         <v>9</v>
@@ -1178,31 +1253,31 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
         <v>9</v>
@@ -1216,7 +1291,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1228,7 +1303,7 @@
         <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F20" t="s">
         <v>6</v>
@@ -1254,7 +1329,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B21" t="s">
         <v>2</v>
@@ -1266,22 +1341,22 @@
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F21" t="s">
         <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" t="s">
         <v>9</v>
       </c>
       <c r="J21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
         <v>9</v>
@@ -1292,31 +1367,31 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" t="s">
         <v>19</v>
       </c>
-      <c r="E22" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" t="s">
-        <v>17</v>
-      </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J22" t="s">
         <v>9</v>
@@ -1330,34 +1405,34 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
         <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
         <v>9</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" t="s">
         <v>9</v>
@@ -1368,7 +1443,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
         <v>2</v>
@@ -1380,7 +1455,7 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F24" t="s">
         <v>6</v>
@@ -1406,7 +1481,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -1418,22 +1493,22 @@
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F25" t="s">
         <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" t="s">
         <v>9</v>
       </c>
       <c r="J25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="s">
         <v>9</v>
@@ -1444,31 +1519,31 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" t="s">
         <v>19</v>
       </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" t="s">
-        <v>17</v>
-      </c>
       <c r="I26" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J26" t="s">
         <v>9</v>
@@ -1482,34 +1557,34 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
         <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I27" t="s">
         <v>9</v>
       </c>
       <c r="J27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" t="s">
         <v>9</v>
@@ -1520,31 +1595,31 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B28" t="s">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" t="s">
         <v>19</v>
       </c>
-      <c r="E28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28" t="s">
-        <v>57</v>
-      </c>
-      <c r="H28" t="s">
-        <v>17</v>
-      </c>
       <c r="I28" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J28" t="s">
         <v>9</v>
@@ -1558,7 +1633,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -1570,16 +1645,16 @@
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" t="s">
         <v>9</v>
@@ -1596,28 +1671,28 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I30" t="s">
         <v>9</v>
@@ -1634,31 +1709,31 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I31" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J31" t="s">
         <v>9</v>
@@ -1672,28 +1747,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" t="s">
         <v>9</v>
@@ -1710,28 +1785,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
         <v>9</v>
@@ -1748,31 +1823,31 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I34" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="J34" t="s">
         <v>9</v>
@@ -1786,31 +1861,31 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" t="s">
         <v>25</v>
       </c>
-      <c r="C35" t="s">
-        <v>18</v>
-      </c>
-      <c r="D35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" t="s">
-        <v>22</v>
-      </c>
       <c r="I35" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J35" t="s">
         <v>9</v>
@@ -1824,19 +1899,19 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F36" t="s">
         <v>6</v>
@@ -1862,34 +1937,34 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
         <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I37" t="s">
         <v>9</v>
       </c>
       <c r="J37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K37" t="s">
         <v>9</v>
@@ -1900,31 +1975,31 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="F38" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I38" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s">
         <v>9</v>
@@ -1938,34 +2013,34 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
         <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H39" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I39" t="s">
         <v>9</v>
       </c>
       <c r="J39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K39" t="s">
         <v>9</v>
@@ -1976,22 +2051,22 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
         <v>7</v>
@@ -2000,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="I40" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J40" t="s">
         <v>9</v>
@@ -2014,31 +2089,31 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
         <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I41" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J41" t="s">
         <v>9</v>
@@ -2052,31 +2127,31 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F42" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I42" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="J42" t="s">
         <v>9</v>
@@ -2090,31 +2165,31 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G43" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H43" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I43" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J43" t="s">
         <v>9</v>
@@ -2128,28 +2203,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="G44" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s">
         <v>9</v>
@@ -2166,28 +2241,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F45" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I45" t="s">
         <v>9</v>
@@ -2204,31 +2279,31 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F46" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I46" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J46" t="s">
         <v>9</v>
@@ -2242,31 +2317,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G47" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="J47" t="s">
         <v>9</v>
@@ -2280,31 +2355,31 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
         <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F48" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G48" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I48" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="J48" t="s">
         <v>9</v>
@@ -2318,31 +2393,31 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F49" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="G49" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I49" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="J49" t="s">
         <v>9</v>
@@ -2356,31 +2431,31 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E50" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="J50" t="s">
         <v>9</v>
@@ -2394,31 +2469,31 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F51" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="G51" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I51" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="J51" t="s">
         <v>9</v>
@@ -2432,31 +2507,31 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F52" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G52" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="H52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -2470,31 +2545,31 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F53" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="H53" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="I53" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="J53" t="s">
         <v>9</v>
@@ -2508,31 +2583,31 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E54" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="F54" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G54" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H54" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="J54" t="s">
         <v>9</v>
@@ -2546,31 +2621,31 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G55" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J55" t="s">
         <v>9</v>
@@ -2584,31 +2659,31 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F56" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G56" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I56" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J56" t="s">
         <v>9</v>
@@ -2622,31 +2697,31 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C57" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" t="s">
+        <v>137</v>
+      </c>
+      <c r="F57" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" t="s">
+        <v>126</v>
+      </c>
+      <c r="H57" t="s">
+        <v>19</v>
+      </c>
+      <c r="I57" t="s">
         <v>99</v>
-      </c>
-      <c r="C57" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E57" t="s">
-        <v>119</v>
-      </c>
-      <c r="F57" t="s">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s">
-        <v>108</v>
-      </c>
-      <c r="H57" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" t="s">
-        <v>81</v>
       </c>
       <c r="J57" t="s">
         <v>9</v>
@@ -2660,31 +2735,31 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F58" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="G58" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="H58" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="I58" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="J58" t="s">
         <v>9</v>
@@ -2698,34 +2773,34 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B59" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C59" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="H59" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I59" t="s">
         <v>9</v>
       </c>
       <c r="J59" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="s">
         <v>9</v>
@@ -2736,22 +2811,22 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F60" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="G60" t="s">
         <v>7</v>
@@ -2760,7 +2835,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -2774,31 +2849,31 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F61" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I61" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="J61" t="s">
         <v>9</v>
@@ -2812,31 +2887,31 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F62" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="G62" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="J62" t="s">
         <v>9</v>
@@ -2850,31 +2925,31 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>140</v>
+      </c>
+      <c r="B63" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" t="s">
+        <v>142</v>
+      </c>
+      <c r="F63" t="s">
         <v>122</v>
       </c>
-      <c r="B63" t="s">
-        <v>123</v>
-      </c>
-      <c r="C63" t="s">
-        <v>18</v>
-      </c>
-      <c r="D63" t="s">
-        <v>26</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" t="s">
+        <v>25</v>
+      </c>
+      <c r="I63" t="s">
         <v>124</v>
-      </c>
-      <c r="F63" t="s">
-        <v>104</v>
-      </c>
-      <c r="G63" t="s">
-        <v>21</v>
-      </c>
-      <c r="H63" t="s">
-        <v>22</v>
-      </c>
-      <c r="I63" t="s">
-        <v>106</v>
       </c>
       <c r="J63" t="s">
         <v>9</v>
@@ -2888,22 +2963,22 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F64" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G64" t="s">
         <v>7</v>
@@ -2912,7 +2987,7 @@
         <v>8</v>
       </c>
       <c r="I64" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J64" t="s">
         <v>9</v>
@@ -2926,31 +3001,31 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B65" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
       </c>
       <c r="D65" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F65" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G65" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I65" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J65" t="s">
         <v>9</v>
@@ -2964,31 +3039,31 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D66" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E66" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F66" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I66" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="J66" t="s">
         <v>9</v>
@@ -3002,31 +3077,31 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E67" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F67" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G67" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H67" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I67" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J67" t="s">
         <v>9</v>
@@ -3040,7 +3115,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
@@ -3052,7 +3127,7 @@
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -3078,7 +3153,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
@@ -3090,22 +3165,22 @@
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H69" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I69" t="s">
         <v>9</v>
       </c>
       <c r="J69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K69" t="s">
         <v>9</v>
@@ -3116,31 +3191,31 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D70" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" t="s">
+        <v>150</v>
+      </c>
+      <c r="F70" t="s">
+        <v>62</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" t="s">
         <v>19</v>
       </c>
-      <c r="E70" t="s">
-        <v>130</v>
-      </c>
-      <c r="F70" t="s">
-        <v>50</v>
-      </c>
-      <c r="G70" t="s">
-        <v>16</v>
-      </c>
-      <c r="H70" t="s">
-        <v>17</v>
-      </c>
       <c r="I70" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J70" t="s">
         <v>9</v>
@@ -3154,34 +3229,34 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
       </c>
       <c r="G71" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I71" t="s">
         <v>9</v>
       </c>
       <c r="J71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K71" t="s">
         <v>9</v>
@@ -3192,7 +3267,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -3204,22 +3279,22 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="F72" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="G72" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="H72" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="I72" t="s">
         <v>9</v>
       </c>
       <c r="J72" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="K72" t="s">
         <v>9</v>
@@ -3230,7 +3305,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s">
         <v>2</v>
@@ -3239,22 +3314,22 @@
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="F73" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="G73" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="H73" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I73" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="J73" t="s">
         <v>9</v>
@@ -3268,31 +3343,31 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B74" t="s">
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
+        <v>21</v>
+      </c>
+      <c r="E74" t="s">
+        <v>161</v>
+      </c>
+      <c r="F74" t="s">
+        <v>162</v>
+      </c>
+      <c r="G74" t="s">
+        <v>163</v>
+      </c>
+      <c r="H74" t="s">
         <v>19</v>
       </c>
-      <c r="E74" t="s">
-        <v>132</v>
-      </c>
-      <c r="F74" t="s">
-        <v>139</v>
-      </c>
-      <c r="G74" t="s">
-        <v>140</v>
-      </c>
-      <c r="H74" t="s">
-        <v>17</v>
-      </c>
       <c r="I74" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="J74" t="s">
         <v>9</v>
@@ -3306,31 +3381,31 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F75" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="G75" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="H75" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I75" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="J75" t="s">
         <v>9</v>
@@ -3344,31 +3419,31 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D76" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="F76" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="G76" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I76" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="J76" t="s">
         <v>9</v>
@@ -3382,19 +3457,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="B77" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -3420,34 +3495,34 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="B78" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H78" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I78" t="s">
         <v>9</v>
       </c>
       <c r="J78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K78" t="s">
         <v>9</v>
@@ -3458,34 +3533,34 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="B79" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" t="s">
+        <v>173</v>
+      </c>
+      <c r="F79" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" t="s">
+        <v>19</v>
+      </c>
+      <c r="I79" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" t="s">
         <v>15</v>
-      </c>
-      <c r="D79" t="s">
-        <v>26</v>
-      </c>
-      <c r="E79" t="s">
-        <v>148</v>
-      </c>
-      <c r="F79" t="s">
-        <v>9</v>
-      </c>
-      <c r="G79" t="s">
-        <v>16</v>
-      </c>
-      <c r="H79" t="s">
-        <v>17</v>
-      </c>
-      <c r="I79" t="s">
-        <v>9</v>
-      </c>
-      <c r="J79" t="s">
-        <v>14</v>
       </c>
       <c r="K79" t="s">
         <v>9</v>
@@ -3496,31 +3571,31 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="B80" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D80" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" t="s">
+        <v>173</v>
+      </c>
+      <c r="F80" t="s">
+        <v>23</v>
+      </c>
+      <c r="G80" t="s">
+        <v>24</v>
+      </c>
+      <c r="H80" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" t="s">
         <v>26</v>
-      </c>
-      <c r="E80" t="s">
-        <v>148</v>
-      </c>
-      <c r="F80" t="s">
-        <v>20</v>
-      </c>
-      <c r="G80" t="s">
-        <v>21</v>
-      </c>
-      <c r="H80" t="s">
-        <v>22</v>
-      </c>
-      <c r="I80" t="s">
-        <v>23</v>
       </c>
       <c r="J80" t="s">
         <v>9</v>
@@ -3534,19 +3609,19 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="B81" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C81" t="s">
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -3572,34 +3647,34 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="B82" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H82" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I82" t="s">
         <v>9</v>
       </c>
       <c r="J82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K82" t="s">
         <v>9</v>
@@ -3610,34 +3685,34 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" t="s">
+        <v>175</v>
+      </c>
+      <c r="F83" t="s">
+        <v>9</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+      <c r="H83" t="s">
+        <v>19</v>
+      </c>
+      <c r="I83" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" t="s">
         <v>15</v>
-      </c>
-      <c r="D83" t="s">
-        <v>26</v>
-      </c>
-      <c r="E83" t="s">
-        <v>150</v>
-      </c>
-      <c r="F83" t="s">
-        <v>9</v>
-      </c>
-      <c r="G83" t="s">
-        <v>16</v>
-      </c>
-      <c r="H83" t="s">
-        <v>17</v>
-      </c>
-      <c r="I83" t="s">
-        <v>9</v>
-      </c>
-      <c r="J83" t="s">
-        <v>14</v>
       </c>
       <c r="K83" t="s">
         <v>9</v>
@@ -3648,31 +3723,31 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="B84" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" t="s">
+        <v>175</v>
+      </c>
+      <c r="F84" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" t="s">
         <v>26</v>
-      </c>
-      <c r="E84" t="s">
-        <v>150</v>
-      </c>
-      <c r="F84" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" t="s">
-        <v>21</v>
-      </c>
-      <c r="H84" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" t="s">
-        <v>23</v>
       </c>
       <c r="J84" t="s">
         <v>9</v>
@@ -3686,19 +3761,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B85" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C85" t="s">
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -3724,34 +3799,34 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B86" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
       </c>
       <c r="D86" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H86" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I86" t="s">
         <v>9</v>
       </c>
       <c r="J86" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K86" t="s">
         <v>9</v>
@@ -3762,34 +3837,34 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B87" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C87" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" t="s">
+        <v>29</v>
+      </c>
+      <c r="E87" t="s">
+        <v>178</v>
+      </c>
+      <c r="F87" t="s">
+        <v>9</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" t="s">
         <v>15</v>
-      </c>
-      <c r="D87" t="s">
-        <v>26</v>
-      </c>
-      <c r="E87" t="s">
-        <v>153</v>
-      </c>
-      <c r="F87" t="s">
-        <v>9</v>
-      </c>
-      <c r="G87" t="s">
-        <v>16</v>
-      </c>
-      <c r="H87" t="s">
-        <v>17</v>
-      </c>
-      <c r="I87" t="s">
-        <v>9</v>
-      </c>
-      <c r="J87" t="s">
-        <v>14</v>
       </c>
       <c r="K87" t="s">
         <v>9</v>
@@ -3800,31 +3875,31 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="B88" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C88" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D88" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" t="s">
+        <v>178</v>
+      </c>
+      <c r="F88" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" t="s">
         <v>26</v>
-      </c>
-      <c r="E88" t="s">
-        <v>153</v>
-      </c>
-      <c r="F88" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" t="s">
-        <v>21</v>
-      </c>
-      <c r="H88" t="s">
-        <v>22</v>
-      </c>
-      <c r="I88" t="s">
-        <v>23</v>
       </c>
       <c r="J88" t="s">
         <v>9</v>
@@ -3838,22 +3913,22 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C89" t="s">
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="F89" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G89" t="s">
         <v>7</v>
@@ -3862,7 +3937,7 @@
         <v>8</v>
       </c>
       <c r="I89" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J89" t="s">
         <v>9</v>
@@ -3876,31 +3951,31 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B90" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
       </c>
       <c r="D90" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="F90" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G90" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I90" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J90" t="s">
         <v>9</v>
@@ -3914,31 +3989,31 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D91" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="F91" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G91" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I91" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="J91" t="s">
         <v>9</v>
@@ -3952,31 +4027,31 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B92" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C92" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="F92" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H92" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I92" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J92" t="s">
         <v>9</v>
@@ -3990,19 +4065,19 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C93" t="s">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -4028,34 +4103,34 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B94" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
       </c>
       <c r="D94" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
       </c>
       <c r="G94" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H94" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I94" t="s">
         <v>9</v>
       </c>
       <c r="J94" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K94" t="s">
         <v>9</v>
@@ -4066,31 +4141,31 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B95" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="F95" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G95" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H95" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I95" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="J95" t="s">
         <v>9</v>
@@ -4104,34 +4179,34 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B96" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="F96" t="s">
         <v>9</v>
       </c>
       <c r="G96" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H96" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I96" t="s">
         <v>9</v>
       </c>
       <c r="J96" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K96" t="s">
         <v>9</v>
@@ -4142,22 +4217,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C97" t="s">
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F97" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G97" t="s">
         <v>7</v>
@@ -4166,7 +4241,7 @@
         <v>8</v>
       </c>
       <c r="I97" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="J97" t="s">
         <v>9</v>
@@ -4180,31 +4255,31 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B98" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
       </c>
       <c r="D98" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F98" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G98" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
@@ -4218,31 +4293,31 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B99" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F99" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G99" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H99" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I99" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="J99" t="s">
         <v>9</v>
@@ -4256,31 +4331,31 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B100" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="C100" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E100" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F100" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G100" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H100" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I100" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J100" t="s">
         <v>9</v>
@@ -4302,42 +4377,42 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/kbl/teaching/qt-intent-sample.xlsx
+++ b/kbl/teaching/qt-intent-sample.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
   <si>
     <t xml:space="preserve">undefined</t>
   </si>
@@ -365,39 +365,48 @@
     <t xml:space="preserve">statistics</t>
   </si>
   <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「分类的含义」（根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「理解」在fill题型认知区间[了解/理解/应用]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、classify、judge。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于fill认知区间[了解/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「分类的含义」（根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）；题型限定：不承载完整的书写与计算过程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在choice题型认知区间[认识/理解/应用]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：apply、classify、fill、judge。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；classify属分类整理而本题型属辨认判断</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于choice认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「分类的含义」（根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「理解」在apply题型认知区间[理解/应用/分析]内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同 KP 其他允许题型：choice、classify、fill、judge。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；classify属分类整理而本题型属综合应用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">成立：认知层级「理解」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">classify</t>
+  </si>
+  <si>
     <t xml:space="preserve">训练「分类的含义」（分类与整理 · 根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）：根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏</t>
   </si>
   <si>
-    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「理解」在fill题型认知区间[了解/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、classify、judge。本题型差异——apply属综合应用而本题型属书面表达；choice属辨认判断而本题型属书面表达；choice含干扰项（辨认成分重）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于fill认知区间[了解/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在choice题型认知区间[认识/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、classify、fill、judge。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；classify属分类整理而本题型属辨认判断</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于choice认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「理解」在apply题型认知区间[理解/应用/分析]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：choice、classify、fill、judge。本题型差异——choice属辨认判断而本题型属综合应用；choice含干扰项（辨认成分重）；classify属分类整理而本题型属综合应用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「理解」落于apply认知区间[理解/应用/分析]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">classify</t>
-  </si>
-  <si>
     <t xml:space="preserve">classify（分类整理题，分类整理）选取依据——认知匹配：本知识点认知层级「理解」在classify题型认知区间[认识/理解/应用]内</t>
   </si>
   <si>
@@ -410,6 +419,9 @@
     <t xml:space="preserve">成立：认知层级「理解」落于classify认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
   </si>
   <si>
+    <t xml:space="preserve">通过judge（判断题）训练特征与关系的正误辨析，对象为「分类的含义」（根据事物的共同特征（颜色、形状、用途等）将物体有序分组，做到不重复、不遗漏）；题型限定：不承载操作性任务与多步应用</t>
+  </si>
+  <si>
     <t xml:space="preserve">judge（判断题，辨认判断）选取依据——认知匹配：本知识点认知层级「理解」在judge题型认知区间[认识/理解]内</t>
   </si>
   <si>
@@ -422,6 +434,15 @@
     <t xml:space="preserve">math-g2-up-u01-k002</t>
   </si>
   <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「单一标准分类」（先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「单一标准分类」（先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组）；题型限定：不承载完整的书写与计算过程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「单一标准分类」（先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
     <t xml:space="preserve">训练「单一标准分类」（分类与整理 · 先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组。）：先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组</t>
   </si>
   <si>
@@ -429,6 +450,9 @@
   </si>
   <si>
     <t xml:space="preserve">成立：认知层级「应用」落于classify认知区间[认识/理解/应用]，数值表征与题型形态兼容；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过judge（判断题）训练特征与关系的正误辨析，对象为「单一标准分类」（先确定分类依据（如“按形状分”），逐一对物体判断归类，再检查是否所有物体都已分组）；题型限定：不承载操作性任务与多步应用</t>
   </si>
   <si>
     <t xml:space="preserve">math-g2-down-u02-k001</t>
@@ -2481,19 +2505,19 @@
         <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H51" t="s">
         <v>25</v>
       </c>
       <c r="I51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J51" t="s">
         <v>9</v>
@@ -2519,19 +2543,19 @@
         <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F52" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G52" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H52" t="s">
         <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J52" t="s">
         <v>9</v>
@@ -2551,25 +2575,25 @@
         <v>117</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D53" t="s">
         <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F53" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G53" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H53" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I53" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J53" t="s">
         <v>9</v>
@@ -2595,19 +2619,19 @@
         <v>29</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F54" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G54" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H54" t="s">
         <v>42</v>
       </c>
       <c r="I54" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J54" t="s">
         <v>9</v>
@@ -2621,7 +2645,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B55" t="s">
         <v>117</v>
@@ -2633,7 +2657,7 @@
         <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F55" t="s">
         <v>96</v>
@@ -2659,7 +2683,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
         <v>117</v>
@@ -2671,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F56" t="s">
         <v>100</v>
       </c>
       <c r="G56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H56" t="s">
         <v>25</v>
@@ -2697,7 +2721,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B57" t="s">
         <v>117</v>
@@ -2709,13 +2733,13 @@
         <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F57" t="s">
         <v>98</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H57" t="s">
         <v>19</v>
@@ -2735,31 +2759,31 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B58" t="s">
         <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D58" t="s">
         <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F58" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G58" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H58" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I58" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J58" t="s">
         <v>9</v>
@@ -2773,7 +2797,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B59" t="s">
         <v>117</v>
@@ -2785,13 +2809,13 @@
         <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="F59" t="s">
         <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H59" t="s">
         <v>42</v>
@@ -2811,10 +2835,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B60" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C60" t="s">
         <v>3</v>
@@ -2823,10 +2847,10 @@
         <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F60" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="G60" t="s">
         <v>7</v>
@@ -2835,7 +2859,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J60" t="s">
         <v>9</v>
@@ -2849,10 +2873,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
@@ -2861,7 +2885,7 @@
         <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F61" t="s">
         <v>119</v>
@@ -2887,10 +2911,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C62" t="s">
         <v>16</v>
@@ -2899,10 +2923,10 @@
         <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F62" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G62" t="s">
         <v>18</v>
@@ -2911,7 +2935,7 @@
         <v>19</v>
       </c>
       <c r="I62" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J62" t="s">
         <v>9</v>
@@ -2925,10 +2949,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
         <v>20</v>
@@ -2937,10 +2961,10 @@
         <v>29</v>
       </c>
       <c r="E63" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="F63" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G63" t="s">
         <v>24</v>
@@ -2949,7 +2973,7 @@
         <v>25</v>
       </c>
       <c r="I63" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
         <v>9</v>
@@ -2963,10 +2987,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
@@ -2975,7 +2999,7 @@
         <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F64" t="s">
         <v>94</v>
@@ -3001,10 +3025,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C65" t="s">
         <v>11</v>
@@ -3013,7 +3037,7 @@
         <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F65" t="s">
         <v>96</v>
@@ -3039,10 +3063,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C66" t="s">
         <v>16</v>
@@ -3051,7 +3075,7 @@
         <v>29</v>
       </c>
       <c r="E66" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F66" t="s">
         <v>98</v>
@@ -3077,10 +3101,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C67" t="s">
         <v>20</v>
@@ -3089,7 +3113,7 @@
         <v>29</v>
       </c>
       <c r="E67" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F67" t="s">
         <v>100</v>
@@ -3115,7 +3139,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
@@ -3127,7 +3151,7 @@
         <v>4</v>
       </c>
       <c r="E68" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -3153,7 +3177,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
@@ -3165,7 +3189,7 @@
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F69" t="s">
         <v>9</v>
@@ -3191,7 +3215,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
@@ -3203,7 +3227,7 @@
         <v>21</v>
       </c>
       <c r="E70" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F70" t="s">
         <v>62</v>
@@ -3229,7 +3253,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
@@ -3241,7 +3265,7 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F71" t="s">
         <v>9</v>
@@ -3267,7 +3291,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
@@ -3279,22 +3303,22 @@
         <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F72" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="G72" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="H72" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I72" t="s">
         <v>9</v>
       </c>
       <c r="J72" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K72" t="s">
         <v>9</v>
@@ -3305,7 +3329,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B73" t="s">
         <v>2</v>
@@ -3317,13 +3341,13 @@
         <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F73" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G73" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H73" t="s">
         <v>14</v>
@@ -3343,7 +3367,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
         <v>2</v>
@@ -3355,13 +3379,13 @@
         <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F74" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="G74" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H74" t="s">
         <v>19</v>
@@ -3381,7 +3405,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
@@ -3393,13 +3417,13 @@
         <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F75" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G75" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="H75" t="s">
         <v>25</v>
@@ -3419,7 +3443,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
@@ -3431,19 +3455,19 @@
         <v>21</v>
       </c>
       <c r="E76" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="F76" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G76" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="H76" t="s">
         <v>33</v>
       </c>
       <c r="I76" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="J76" t="s">
         <v>9</v>
@@ -3457,10 +3481,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
@@ -3469,7 +3493,7 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -3495,10 +3519,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
@@ -3507,7 +3531,7 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
@@ -3533,10 +3557,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B79" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C79" t="s">
         <v>16</v>
@@ -3545,7 +3569,7 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F79" t="s">
         <v>9</v>
@@ -3571,10 +3595,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
@@ -3583,7 +3607,7 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F80" t="s">
         <v>23</v>
@@ -3609,10 +3633,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
         <v>3</v>
@@ -3621,7 +3645,7 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -3647,10 +3671,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B82" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -3659,7 +3683,7 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
@@ -3685,10 +3709,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
         <v>16</v>
@@ -3697,7 +3721,7 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -3723,10 +3747,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B84" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
@@ -3735,7 +3759,7 @@
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="F84" t="s">
         <v>23</v>
@@ -3761,10 +3785,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C85" t="s">
         <v>3</v>
@@ -3773,7 +3797,7 @@
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -3799,10 +3823,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C86" t="s">
         <v>11</v>
@@ -3811,7 +3835,7 @@
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
@@ -3837,10 +3861,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
         <v>16</v>
@@ -3849,7 +3873,7 @@
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F87" t="s">
         <v>9</v>
@@ -3875,10 +3899,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C88" t="s">
         <v>20</v>
@@ -3887,7 +3911,7 @@
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F88" t="s">
         <v>23</v>
@@ -3913,10 +3937,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B89" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C89" t="s">
         <v>3</v>
@@ -3925,7 +3949,7 @@
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F89" t="s">
         <v>94</v>
@@ -3951,10 +3975,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -3963,7 +3987,7 @@
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F90" t="s">
         <v>96</v>
@@ -3989,10 +4013,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C91" t="s">
         <v>16</v>
@@ -4001,7 +4025,7 @@
         <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F91" t="s">
         <v>98</v>
@@ -4027,10 +4051,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -4039,7 +4063,7 @@
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F92" t="s">
         <v>100</v>
@@ -4065,10 +4089,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B93" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C93" t="s">
         <v>3</v>
@@ -4077,7 +4101,7 @@
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -4103,10 +4127,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B94" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
         <v>11</v>
@@ -4115,7 +4139,7 @@
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F94" t="s">
         <v>9</v>
@@ -4141,10 +4165,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
@@ -4153,7 +4177,7 @@
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F95" t="s">
         <v>62</v>
@@ -4179,10 +4203,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C96" t="s">
         <v>20</v>
@@ -4191,7 +4215,7 @@
         <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F96" t="s">
         <v>9</v>
@@ -4217,10 +4241,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B97" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C97" t="s">
         <v>3</v>
@@ -4229,7 +4253,7 @@
         <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F97" t="s">
         <v>94</v>
@@ -4255,10 +4279,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -4267,7 +4291,7 @@
         <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F98" t="s">
         <v>96</v>
@@ -4293,10 +4317,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B99" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C99" t="s">
         <v>16</v>
@@ -4305,7 +4329,7 @@
         <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F99" t="s">
         <v>98</v>
@@ -4331,10 +4355,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B100" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="C100" t="s">
         <v>20</v>
@@ -4343,7 +4367,7 @@
         <v>29</v>
       </c>
       <c r="E100" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F100" t="s">
         <v>100</v>
@@ -4377,42 +4401,42 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/kbl/teaching/qt-intent-sample.xlsx
+++ b/kbl/teaching/qt-intent-sample.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t xml:space="preserve">undefined</t>
   </si>
@@ -491,61 +491,19 @@
     <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「解决问题」（能运用有余数除法解决实际问题，并结合生活实际进行判断和取舍，进一法：租船、乘车、装箱（剩余也要多一份））；题型限定：不承载完整的书写与计算过程</t>
   </si>
   <si>
-    <t xml:space="preserve">math-g2-down-u02-k005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载概念表述与图形操作</t>
-  </si>
-  <si>
-    <t xml:space="preserve">calc（计算题，计算操作）选取依据——认知匹配：本知识点认知层级「应用」在calc题型认知区间[了解/理解/应用]内</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、choice、fill、geometry。本题型差异——apply属综合应用而本题型属计算操作；apply支持图形；choice属辨认判断而本题型属计算操作</t>
-  </si>
-  <si>
-    <t xml:space="preserve">风险（calc）：题面退化为纯算式，知识点语义情境丢失（算对≠理解该知识的意义）；表征冲突：本知识点含图形表征而该题型不支持图形，图形语义将降级为文字/算式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">representation-conflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载多步推理的完整表述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fill（填空题，书面表达）选取依据——认知匹配：本知识点认知层级「应用」在fill题型认知区间[了解/理解/应用]内；表征支持：本知识点含图形表征，fill题型支持图形呈现</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、calc、choice、geometry。本题型差异——apply属综合应用而本题型属书面表达；calc属计算操作而本题型属书面表达；calc仅文字/算式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载方法定义的复述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apply（解决问题/应用题，综合应用）选取依据——认知匹配：本知识点认知层级「应用」在apply题型认知区间[理解/应用/分析]内；表征支持：本知识点含图形表征，apply题型支持图形呈现</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：calc、choice、fill、geometry。本题型差异——calc属计算操作而本题型属综合应用；calc仅文字/算式；choice属辨认判断而本题型属综合应用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载完整的书写与计算过程</t>
-  </si>
-  <si>
-    <t xml:space="preserve">choice（选择题，辨认判断）选取依据——认知匹配：本知识点认知层级「应用」在choice题型认知区间[认识/理解/应用]内；表征支持：本知识点含图形表征，choice题型支持图形呈现</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、calc、fill、geometry。本题型差异——apply属综合应用而本题型属辨认判断；apply无干扰项（需独立产出）；calc属计算操作而本题型属辨认判断</t>
-  </si>
-  <si>
-    <t xml:space="preserve">通过geometry（操作/作图题）训练图形操作与直观辨认，对象为「周期问题」（利用有余数除法找图形、彩旗排列规律）；题型限定：不承载脱离图形的纯文字表述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">geometry（操作/作图题，图形操作）选取依据——认知匹配：本知识点认知层级「应用」在geometry题型认知区间[认识/理解/应用/分析]内；表征支持：本知识点含图形表征，geometry题型支持图形呈现</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同 KP 其他允许题型：apply、calc、choice、fill。本题型差异——apply属综合应用而本题型属图形操作；apply带情境；apply认知跨度[理解/应用/分析]与本题型[认识/理解/应用/分析]不同</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成立：认知层级「应用」落于geometry认知区间[认识/理解/应用/分析]，图形表征获支持；配合 driftRisk 所列风险的命题侧规避，该 KP×题型组合具备教育正当性</t>
+    <t xml:space="preserve">math-g2-down-u03-k003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过calc（计算题）训练计算过程与得数产出，对象为「倍的认识」（圈一圈，理解 “几倍” 就是几份）；题型限定：不承载概念表述与图形操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过fill（填空题）训练关键步骤与结果的书面表达，对象为「倍的认识」（圈一圈，理解 “几倍” 就是几份）；题型限定：不承载多步推理的完整表述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过apply（解决问题/应用题）训练在情境中运用与迁移，对象为「倍的认识」（圈一圈，理解 “几倍” 就是几份）；题型限定：不承载方法定义的复述</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通过choice（选择题）训练辨认、对应与辨析（在干扰项下做出正确选择），对象为「倍的认识」（圈一圈，理解 “几倍” 就是几份）；题型限定：不承载完整的书写与计算过程</t>
   </si>
   <si>
     <t xml:space="preserve">math-g3-up-u08-k001</t>
@@ -3306,19 +3264,19 @@
         <v>161</v>
       </c>
       <c r="F72" t="s">
-        <v>162</v>
+        <v>6</v>
       </c>
       <c r="G72" t="s">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="H72" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="I72" t="s">
         <v>9</v>
       </c>
       <c r="J72" t="s">
-        <v>165</v>
+        <v>10</v>
       </c>
       <c r="K72" t="s">
         <v>9</v>
@@ -3338,25 +3296,25 @@
         <v>11</v>
       </c>
       <c r="D73" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E73" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F73" t="s">
-        <v>167</v>
+        <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="H73" t="s">
         <v>14</v>
       </c>
       <c r="I73" t="s">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="J73" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K73" t="s">
         <v>9</v>
@@ -3376,25 +3334,25 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E74" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F74" t="s">
-        <v>170</v>
+        <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="H74" t="s">
         <v>19</v>
       </c>
       <c r="I74" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="J74" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K74" t="s">
         <v>9</v>
@@ -3417,19 +3375,19 @@
         <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F75" t="s">
-        <v>173</v>
+        <v>23</v>
       </c>
       <c r="G75" t="s">
-        <v>174</v>
+        <v>24</v>
       </c>
       <c r="H75" t="s">
         <v>25</v>
       </c>
       <c r="I75" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="J75" t="s">
         <v>9</v>
@@ -3443,34 +3401,34 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B76" t="s">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F76" t="s">
-        <v>176</v>
+        <v>6</v>
       </c>
       <c r="G76" t="s">
-        <v>177</v>
+        <v>7</v>
       </c>
       <c r="H76" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="I76" t="s">
-        <v>178</v>
+        <v>9</v>
       </c>
       <c r="J76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K76" t="s">
         <v>9</v>
@@ -3481,34 +3439,34 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B77" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C77" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="F77" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H77" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I77" t="s">
         <v>9</v>
       </c>
       <c r="J77" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K77" t="s">
         <v>9</v>
@@ -3519,28 +3477,28 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B78" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="F78" t="s">
         <v>9</v>
       </c>
       <c r="G78" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H78" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I78" t="s">
         <v>9</v>
@@ -3557,34 +3515,34 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D79" t="s">
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="F79" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H79" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I79" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J79" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K79" t="s">
         <v>9</v>
@@ -3595,34 +3553,34 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D80" t="s">
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F80" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G80" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H80" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I80" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J80" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K80" t="s">
         <v>9</v>
@@ -3633,34 +3591,34 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D81" t="s">
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F81" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G81" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H81" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I81" t="s">
         <v>9</v>
       </c>
       <c r="J81" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K81" t="s">
         <v>9</v>
@@ -3671,28 +3629,28 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C82" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D82" t="s">
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F82" t="s">
         <v>9</v>
       </c>
       <c r="G82" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H82" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I82" t="s">
         <v>9</v>
@@ -3709,34 +3667,34 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F83" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G83" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H83" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I83" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J83" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K83" t="s">
         <v>9</v>
@@ -3747,34 +3705,34 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D84" t="s">
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F84" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G84" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H84" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I84" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J84" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K84" t="s">
         <v>9</v>
@@ -3785,34 +3743,34 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B85" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C85" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D85" t="s">
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F85" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G85" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H85" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I85" t="s">
         <v>9</v>
       </c>
       <c r="J85" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K85" t="s">
         <v>9</v>
@@ -3823,28 +3781,28 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C86" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F86" t="s">
         <v>9</v>
       </c>
       <c r="G86" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H86" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I86" t="s">
         <v>9</v>
@@ -3861,34 +3819,34 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D87" t="s">
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="F87" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G87" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H87" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I87" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J87" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K87" t="s">
         <v>9</v>
@@ -3899,31 +3857,31 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B88" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D88" t="s">
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F88" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="G88" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H88" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="J88" t="s">
         <v>9</v>
@@ -3937,31 +3895,31 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C89" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F89" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G89" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H89" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I89" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J89" t="s">
         <v>9</v>
@@ -3975,31 +3933,31 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B90" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C90" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F90" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G90" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H90" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I90" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J90" t="s">
         <v>9</v>
@@ -4013,31 +3971,31 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D91" t="s">
         <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F91" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G91" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H91" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I91" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J91" t="s">
         <v>9</v>
@@ -4051,34 +4009,34 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C92" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D92" t="s">
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F92" t="s">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="G92" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H92" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I92" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="J92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K92" t="s">
         <v>9</v>
@@ -4089,34 +4047,34 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C93" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D93" t="s">
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F93" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G93" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H93" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I93" t="s">
         <v>9</v>
       </c>
       <c r="J93" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K93" t="s">
         <v>9</v>
@@ -4127,34 +4085,34 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D94" t="s">
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F94" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="G94" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H94" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I94" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="J94" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K94" t="s">
         <v>9</v>
@@ -4165,34 +4123,34 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D95" t="s">
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="F95" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="G95" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H95" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="J95" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K95" t="s">
         <v>9</v>
@@ -4203,34 +4161,34 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C96" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D96" t="s">
         <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F96" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="G96" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H96" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I96" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="J96" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K96" t="s">
         <v>9</v>
@@ -4241,31 +4199,31 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B97" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C97" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D97" t="s">
         <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F97" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G97" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H97" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I97" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J97" t="s">
         <v>9</v>
@@ -4279,31 +4237,31 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C98" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
         <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F98" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G98" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H98" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I98" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J98" t="s">
         <v>9</v>
@@ -4317,31 +4275,31 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D99" t="s">
         <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="F99" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G99" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H99" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I99" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J99" t="s">
         <v>9</v>
@@ -4350,44 +4308,6 @@
         <v>9</v>
       </c>
       <c r="L99" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>192</v>
-      </c>
-      <c r="B100" t="s">
-        <v>190</v>
-      </c>
-      <c r="C100" t="s">
-        <v>20</v>
-      </c>
-      <c r="D100" t="s">
-        <v>29</v>
-      </c>
-      <c r="E100" t="s">
-        <v>193</v>
-      </c>
-      <c r="F100" t="s">
-        <v>100</v>
-      </c>
-      <c r="G100" t="s">
-        <v>24</v>
-      </c>
-      <c r="H100" t="s">
-        <v>25</v>
-      </c>
-      <c r="I100" t="s">
-        <v>101</v>
-      </c>
-      <c r="J100" t="s">
-        <v>9</v>
-      </c>
-      <c r="K100" t="s">
-        <v>9</v>
-      </c>
-      <c r="L100" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4401,42 +4321,42 @@
     <row r="1"/>
     <row r="2">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
